--- a/Subgroups/ASX/Proposed Extension Working Materials/ASX Concept Mapping.xlsx
+++ b/Subgroups/ASX/Proposed Extension Working Materials/ASX Concept Mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michael.dembach\repositories_foreign\hyssostech\C2SIMArtifacts\Subgroups\ASX\Proposed Extension Working Materials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\claude\f--Repos-C2SIM-C2SIMArtifacts\753e84a4-a0af-44d3-a981-1b4e9cb31ee3\scratchpad\wt-typos\Subgroups\ASX\Proposed Extension Working Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDC660C-D2E1-4D17-B4C9-EB17604805DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02936BB1-C6F6-4012-BE11-A0E0BE2932BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{315F412D-A997-402A-95E2-E68C4026AE2E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{315F412D-A997-402A-95E2-E68C4026AE2E}"/>
   </bookViews>
   <sheets>
     <sheet name="All Concepts" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="91">
   <si>
     <t>C2SIM Object</t>
   </si>
@@ -202,9 +202,6 @@
   </si>
   <si>
     <t>Route, Target Database, Hostility Database, Identification Parameters</t>
-  </si>
-  <si>
-    <t>Drone – Fixed Wing, Drone - Hover</t>
   </si>
   <si>
     <t xml:space="preserve">SensorType, Armiture, Supplies (Medical), Supplies (Food), Ammunition, Fuel </t>
@@ -322,7 +319,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,7 +455,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -479,7 +476,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -795,24 +792,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2B7166-F525-4BB1-842E-284B0E2C36F8}">
-  <dimension ref="A1:J53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9140625" defaultRowHeight="14"/>
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.08203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
-    <col min="4" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.4140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.9140625" style="1"/>
+    <col min="1" max="1" width="24.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.08984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.26953125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="20.7265625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.26953125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.36328125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" ht="126">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="148" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>14</v>
@@ -824,22 +821,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I1" s="11" t="s">
         <v>16</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="56">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
@@ -854,15 +851,15 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="56">
-      <c r="A3" s="10" t="s">
-        <v>67</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>23</v>
@@ -875,12 +872,12 @@
       </c>
       <c r="E3" s="10"/>
       <c r="J3" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>40</v>
@@ -893,33 +890,33 @@
       </c>
       <c r="E4" s="10"/>
       <c r="G4" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="56">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>46</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" s="10"/>
       <c r="J5" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="42">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>47</v>
@@ -930,10 +927,10 @@
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="J6" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>49</v>
       </c>
@@ -941,15 +938,15 @@
         <v>18</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="J7" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="28">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>17</v>
       </c>
@@ -957,15 +954,15 @@
         <v>18</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="J8" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="42">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
         <v>19</v>
       </c>
@@ -978,10 +975,10 @@
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="J9" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="42">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>36</v>
       </c>
@@ -994,10 +991,10 @@
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="J10" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="42">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>29</v>
       </c>
@@ -1012,26 +1009,26 @@
       </c>
       <c r="E11" s="10"/>
       <c r="J11" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="42">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="12"/>
       <c r="J12" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="28">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>32</v>
       </c>
@@ -1046,10 +1043,10 @@
       </c>
       <c r="E13" s="12"/>
       <c r="J13" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="28">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>26</v>
       </c>
@@ -1062,330 +1059,298 @@
       </c>
       <c r="E14" s="12"/>
       <c r="J14" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="42">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>38</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E15" s="12"/>
       <c r="J15" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="28.75" customHeight="1">
-      <c r="A16" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>39</v>
-      </c>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="J16" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="56">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="J17" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="28">
-      <c r="A18" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="J18" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="28">
-      <c r="A19" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="J19" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="14.5">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="1:10" ht="14.5">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:10" ht="14.5">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="1:10" ht="14.5">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="C23" s="10"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="1:10" ht="14.5">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="1:10" ht="14.5">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="10"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
     </row>
-    <row r="26" spans="1:10" ht="14.5">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="10"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
     </row>
-    <row r="27" spans="1:10" ht="14.5">
-      <c r="A27" s="9"/>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-    </row>
-    <row r="28" spans="1:10" ht="14.5">
-      <c r="A28" s="9"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="8"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-    </row>
-    <row r="29" spans="1:10" ht="14.5">
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="1:10" ht="14.5">
-      <c r="A30" s="8"/>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="9"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-    </row>
-    <row r="31" spans="1:10" ht="14.5">
-      <c r="A31" s="8"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="9"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-    </row>
-    <row r="32" spans="1:10" ht="14.5">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:5" ht="14.5">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="1:5" ht="14.5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35" spans="1:5" ht="14.5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36" spans="1:5" ht="14.5">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="1:5" ht="14.5">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
     </row>
-    <row r="38" spans="1:5" ht="14.5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
     </row>
-    <row r="39" spans="1:5" ht="14.5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
     </row>
-    <row r="40" spans="1:5" ht="14.5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
     </row>
-    <row r="41" spans="1:5" ht="14.5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
     </row>
-    <row r="42" spans="1:5" ht="14.5">
-      <c r="A42" s="9"/>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="8"/>
       <c r="B42" s="8"/>
-      <c r="C42" s="9"/>
+      <c r="C42" s="8"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
     </row>
-    <row r="43" spans="1:5" ht="14.5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
     </row>
-    <row r="44" spans="1:5" ht="14.5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
+      <c r="B44" s="9"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-    </row>
-    <row r="45" spans="1:5" ht="14.5">
-      <c r="A45" s="9"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="8"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-    </row>
-    <row r="46" spans="1:5" ht="14.5">
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
     </row>
-    <row r="47" spans="1:5" ht="14.5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48" spans="1:5" ht="14.5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
     </row>
-    <row r="49" spans="1:5" ht="14.5">
-      <c r="A49" s="8"/>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="9"/>
       <c r="B49" s="9"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-    </row>
-    <row r="50" spans="1:5" ht="14.5">
-      <c r="A50" s="8"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="9"/>
       <c r="B50" s="9"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-    </row>
-    <row r="51" spans="1:5" ht="14.5">
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
     </row>
-    <row r="52" spans="1:5" ht="14.5">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-    </row>
-    <row r="53" spans="1:5" ht="14.5">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D53">
-    <sortCondition ref="A2:A53"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D51">
+    <sortCondition ref="A2:A51"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -1395,12 +1360,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A8839B-7B04-4264-BEF5-B002CE54D11F}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="25.25" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="25.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="25.25" style="1"/>
+    <col min="1" max="16384" width="25.26953125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18">
+    <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1414,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -1424,51 +1389,51 @@
       </c>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" ht="14.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="14.4">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="14.4">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="14.4">
-      <c r="A5" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="43.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>48</v>
       </c>
@@ -1479,7 +1444,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1490,19 +1455,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C18DA4BD-65F5-4B7D-9E28-58B65E4324DE}">
   <dimension ref="A1:G68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9140625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.08203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.58203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.9140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.90625" style="1" customWidth="1"/>
     <col min="7" max="7" width="38" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.9140625" style="1"/>
+    <col min="8" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="36">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="37" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -1525,55 +1490,55 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:7" ht="14.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:7" ht="14.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:7" ht="14.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:7" ht="14.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:7" ht="14.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="14.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:7" ht="14.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="C9" s="5"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="14.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="C10" s="5"/>
     </row>
-    <row r="15" spans="1:7" ht="14.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
     </row>
-    <row r="18" spans="1:3" ht="14.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="C18" s="3"/>
     </row>
-    <row r="22" spans="1:3" ht="14.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
     </row>
-    <row r="27" spans="1:3" ht="14.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="1:3" ht="14.4">
+    <row r="28" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>12</v>
       </c>
@@ -1581,37 +1546,37 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="14.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:3" ht="21.65" customHeight="1">
+    <row r="32" spans="1:3" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
     </row>
-    <row r="34" spans="1:5" ht="14.4">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="1:5" ht="14.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
     </row>
-    <row r="38" spans="1:5" ht="14.4">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="7"/>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="7"/>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" s="7"/>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="7"/>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
     </row>
   </sheetData>
@@ -1622,12 +1587,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A8E33F-C1AB-4721-ABD8-DAB6B9B4CB63}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="22.58203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="22.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="22.58203125" style="1"/>
+    <col min="1" max="16384" width="22.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18">
+    <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -1659,12 +1624,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41331979-9D39-4390-90C7-8E12A1C4FBDD}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="22.08203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="22.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="22.08203125" style="1"/>
+    <col min="1" max="16384" width="22.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18">
+    <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
